--- a/data/trans_orig/IP18B-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP18B-Provincia-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1856</t>
+          <t>1914</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8372</t>
+          <t>8473</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1422</t>
+          <t>1393</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7960</t>
+          <t>7472</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4394</t>
+          <t>4613</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>13419</t>
+          <t>13149</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>12,86%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>33269</t>
+          <t>33599</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>42791</t>
+          <t>42797</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>66,22%</t>
+          <t>66,88%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>85,17%</t>
+          <t>85,18%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>32658</t>
+          <t>32605</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>43060</t>
+          <t>43168</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>62,78%</t>
+          <t>62,68%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>82,78%</t>
+          <t>82,99%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>69622</t>
+          <t>69868</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>83801</t>
+          <t>83775</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>68,08%</t>
+          <t>68,32%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>81,95%</t>
+          <t>81,93%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3663</t>
+          <t>4087</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11669</t>
+          <t>11648</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>23,18%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>6220</t>
+          <t>5777</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>15446</t>
+          <t>15233</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>29,69%</t>
+          <t>29,28%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>11607</t>
+          <t>11717</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>23843</t>
+          <t>24552</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>23,32%</t>
+          <t>24,01%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2554</t>
+          <t>3095</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>9924</t>
+          <t>10104</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2509</t>
+          <t>2157</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>9453</t>
+          <t>8845</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>5872</t>
+          <t>6287</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>16269</t>
+          <t>16017</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,51%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>66921</t>
+          <t>66208</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>78846</t>
+          <t>78722</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>73,1%</t>
+          <t>72,32%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>86,12%</t>
+          <t>85,99%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>73974</t>
+          <t>75022</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>85713</t>
+          <t>86143</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>76,52%</t>
+          <t>77,6%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>88,66%</t>
+          <t>89,11%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>145240</t>
+          <t>144040</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>162511</t>
+          <t>161516</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>77,16%</t>
+          <t>76,53%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>86,34%</t>
+          <t>85,81%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8144</t>
+          <t>7840</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>18856</t>
+          <t>18943</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>20,69%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7114</t>
+          <t>6827</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>17576</t>
+          <t>16600</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>17452</t>
+          <t>17108</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>32172</t>
+          <t>31439</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>16,7%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1563</t>
+          <t>1464</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8606</t>
+          <t>8342</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>629</t>
+          <t>630</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5059</t>
+          <t>5679</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>3193</t>
+          <t>2774</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>12438</t>
+          <t>10920</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>8,37%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>34599</t>
+          <t>34295</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>46661</t>
+          <t>47283</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>54,62%</t>
+          <t>54,14%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>73,65%</t>
+          <t>74,64%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>48522</t>
+          <t>48290</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>58323</t>
+          <t>58448</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>72,26%</t>
+          <t>71,91%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>86,85%</t>
+          <t>87,04%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>86279</t>
+          <t>85402</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>102636</t>
+          <t>102192</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>66,11%</t>
+          <t>65,44%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>78,65%</t>
+          <t>78,31%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>13020</t>
+          <t>11971</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>24482</t>
+          <t>24578</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>18,9%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>38,65%</t>
+          <t>38,8%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>7389</t>
+          <t>7259</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>16602</t>
+          <t>16759</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>24,72%</t>
+          <t>24,96%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>22656</t>
+          <t>23230</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>38074</t>
+          <t>38210</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>17,8%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>29,17%</t>
+          <t>29,28%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1453</t>
+          <t>1490</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8051</t>
+          <t>8078</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2206</t>
+          <t>2392</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>9106</t>
+          <t>9642</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>14,23%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4980</t>
+          <t>4815</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>14760</t>
+          <t>13878</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>10,27%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>40697</t>
+          <t>41479</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>53130</t>
+          <t>53168</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>60,39%</t>
+          <t>61,55%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>78,83%</t>
+          <t>78,89%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>38875</t>
+          <t>40175</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>51650</t>
+          <t>52272</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>57,36%</t>
+          <t>59,28%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>76,21%</t>
+          <t>77,13%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>85799</t>
+          <t>85625</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>102947</t>
+          <t>102829</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>63,48%</t>
+          <t>63,35%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>76,16%</t>
+          <t>76,07%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>10775</t>
+          <t>11392</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>22424</t>
+          <t>22766</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>16,9%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>33,27%</t>
+          <t>33,78%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>11550</t>
+          <t>10900</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>23274</t>
+          <t>21930</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>34,34%</t>
+          <t>32,36%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>24425</t>
+          <t>24969</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>40147</t>
+          <t>39981</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>18,47%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>29,7%</t>
+          <t>29,58%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>643</t>
+          <t>635</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5619</t>
+          <t>5521</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>17,19%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1355</t>
+          <t>1358</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>6978</t>
+          <t>7019</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>21,23%</t>
+          <t>21,35%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2720</t>
+          <t>2704</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>10312</t>
+          <t>10168</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>15,65%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>15383</t>
+          <t>15148</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>23820</t>
+          <t>24367</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>47,91%</t>
+          <t>47,18%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>74,19%</t>
+          <t>75,89%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>13646</t>
+          <t>13689</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>23065</t>
+          <t>22900</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>41,52%</t>
+          <t>41,65%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>70,17%</t>
+          <t>69,67%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>32342</t>
+          <t>31514</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>45131</t>
+          <t>45010</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>49,77%</t>
+          <t>48,5%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>69,45%</t>
+          <t>69,27%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>6240</t>
+          <t>5721</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>14576</t>
+          <t>14274</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>45,4%</t>
+          <t>44,45%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>6523</t>
+          <t>6577</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>15671</t>
+          <t>16234</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>47,68%</t>
+          <t>49,39%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>14843</t>
+          <t>14679</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>26929</t>
+          <t>27296</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>22,84%</t>
+          <t>22,59%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>41,44%</t>
+          <t>42,01%</t>
         </is>
       </c>
     </row>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>625</t>
+          <t>628</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>5002</t>
+          <t>5399</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3028,12 +3028,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1236</t>
+          <t>1239</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>6924</t>
+          <t>6973</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>13,72%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>2545</t>
+          <t>2524</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>9327</t>
+          <t>9772</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>9,59%</t>
         </is>
       </c>
     </row>
@@ -3126,12 +3126,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>30769</t>
+          <t>30267</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>41169</t>
+          <t>40418</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3141,12 +3141,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>60,21%</t>
+          <t>59,22%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>80,55%</t>
+          <t>79,09%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,12 +3161,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>29370</t>
+          <t>28889</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>39361</t>
+          <t>39252</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3176,12 +3176,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>57,8%</t>
+          <t>56,86%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>77,47%</t>
+          <t>77,25%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,12 +3196,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>63371</t>
+          <t>63551</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>77877</t>
+          <t>78081</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>62,18%</t>
+          <t>62,36%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>76,41%</t>
+          <t>76,61%</t>
         </is>
       </c>
     </row>
@@ -3239,12 +3239,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>8114</t>
+          <t>8622</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>18350</t>
+          <t>18484</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3254,12 +3254,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>35,91%</t>
+          <t>36,17%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,12 +3274,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>8610</t>
+          <t>8488</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>18087</t>
+          <t>18122</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3289,12 +3289,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>16,71%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>35,6%</t>
+          <t>35,67%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>18985</t>
+          <t>18546</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>33227</t>
+          <t>32897</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>32,6%</t>
+          <t>32,28%</t>
         </is>
       </c>
     </row>
@@ -3469,12 +3469,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1336</t>
+          <t>1309</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>7632</t>
+          <t>6952</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3484,47 +3484,47 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
+          <t>1,08%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>5,72%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>4093</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>1364</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>8190</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>3,3%</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
           <t>1,1%</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>6,28%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>4093</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>1424</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>8315</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>3,3%</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>1,15%</t>
-        </is>
-      </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3982</t>
+          <t>3543</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>12842</t>
+          <t>13136</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,35%</t>
         </is>
       </c>
     </row>
@@ -3582,12 +3582,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>96376</t>
+          <t>96687</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>108464</t>
+          <t>108617</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3597,12 +3597,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>79,24%</t>
+          <t>79,5%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>89,18%</t>
+          <t>89,31%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>94310</t>
+          <t>93246</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>107509</t>
+          <t>107387</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3632,12 +3632,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>76,15%</t>
+          <t>75,29%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>86,81%</t>
+          <t>86,71%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>194709</t>
+          <t>193116</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>213321</t>
+          <t>213397</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3667,12 +3667,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>79,32%</t>
+          <t>78,67%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>86,9%</t>
+          <t>86,93%</t>
         </is>
       </c>
     </row>
@@ -3695,12 +3695,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>10317</t>
+          <t>10265</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>21365</t>
+          <t>21684</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3710,12 +3710,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>17,83%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>12545</t>
+          <t>12895</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>25230</t>
+          <t>25884</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>20,37%</t>
+          <t>20,9%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>25382</t>
+          <t>25490</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>42520</t>
+          <t>42740</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>17,41%</t>
         </is>
       </c>
     </row>
@@ -3925,12 +3925,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>6615</t>
+          <t>5867</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>16593</t>
+          <t>16370</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3940,12 +3940,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>4485</t>
+          <t>4386</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>13460</t>
+          <t>13324</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3975,12 +3975,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>12763</t>
+          <t>11912</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>25927</t>
+          <t>25381</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4010,12 +4010,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>9,91%</t>
         </is>
       </c>
     </row>
@@ -4038,12 +4038,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>79312</t>
+          <t>79475</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>94879</t>
+          <t>95335</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4053,47 +4053,47 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
+          <t>65,53%</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>78,6%</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>147</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>95771</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>88182</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>103596</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>71,01%</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
           <t>65,39%</t>
         </is>
       </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>78,23%</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>147</t>
-        </is>
-      </c>
-      <c r="K33" s="2" t="inlineStr">
-        <is>
-          <t>95771</t>
-        </is>
-      </c>
-      <c r="L33" s="2" t="inlineStr">
-        <is>
-          <t>87073</t>
-        </is>
-      </c>
-      <c r="M33" s="2" t="inlineStr">
-        <is>
-          <t>103705</t>
-        </is>
-      </c>
-      <c r="N33" s="2" t="inlineStr">
-        <is>
-          <t>71,01%</t>
-        </is>
-      </c>
-      <c r="O33" s="2" t="inlineStr">
-        <is>
-          <t>64,56%</t>
-        </is>
-      </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>76,9%</t>
+          <t>76,82%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4108,12 +4108,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>171879</t>
+          <t>171450</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>193693</t>
+          <t>194515</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4123,12 +4123,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>67,1%</t>
+          <t>66,93%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>75,62%</t>
+          <t>75,94%</t>
         </is>
       </c>
     </row>
@@ -4151,12 +4151,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>17309</t>
+          <t>16937</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>30391</t>
+          <t>31005</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4166,12 +4166,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>25,06%</t>
+          <t>25,56%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4186,12 +4186,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>23820</t>
+          <t>23761</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>39308</t>
+          <t>38143</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4201,12 +4201,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>29,15%</t>
+          <t>28,28%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>45071</t>
+          <t>44501</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>65670</t>
+          <t>65328</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4236,12 +4236,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>17,37%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>25,64%</t>
+          <t>25,5%</t>
         </is>
       </c>
     </row>
@@ -4381,12 +4381,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>26487</t>
+          <t>27068</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>44683</t>
+          <t>45931</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4396,12 +4396,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4416,12 +4416,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>26671</t>
+          <t>25496</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>44963</t>
+          <t>44729</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4431,12 +4431,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4451,12 +4451,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>57599</t>
+          <t>58166</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>83626</t>
+          <t>84562</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,9%</t>
         </is>
       </c>
     </row>
@@ -4494,12 +4494,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>429210</t>
+          <t>429125</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>464163</t>
+          <t>462620</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>71,7%</t>
+          <t>71,68%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>77,53%</t>
+          <t>77,28%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4529,12 +4529,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>452444</t>
+          <t>450040</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>484936</t>
+          <t>486568</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4544,12 +4544,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>72,27%</t>
+          <t>71,89%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>77,46%</t>
+          <t>77,73%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4564,12 +4564,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>891477</t>
+          <t>889736</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>940898</t>
+          <t>941094</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>72,79%</t>
+          <t>72,65%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>76,83%</t>
+          <t>76,84%</t>
         </is>
       </c>
     </row>
@@ -4607,12 +4607,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>100459</t>
+          <t>100758</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>132024</t>
+          <t>131838</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4622,12 +4622,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>22,05%</t>
+          <t>22,02%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>107051</t>
+          <t>106322</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>138754</t>
+          <t>138219</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4657,12 +4657,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>16,98%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>22,16%</t>
+          <t>22,08%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>215314</t>
+          <t>215505</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>262744</t>
+          <t>260096</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4692,12 +4692,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>21,45%</t>
+          <t>21,24%</t>
         </is>
       </c>
     </row>
@@ -5073,12 +5073,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>630</t>
+          <t>622</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6369</t>
+          <t>6841</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5088,12 +5088,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5108,12 +5108,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3252</t>
+          <t>3315</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12490</t>
+          <t>12156</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5123,12 +5123,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,16%</t>
+          <t>19,62%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5143,12 +5143,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5245</t>
+          <t>5051</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>15273</t>
+          <t>15681</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>13,64%</t>
         </is>
       </c>
     </row>
@@ -5186,12 +5186,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>31578</t>
+          <t>32004</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>42904</t>
+          <t>43279</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5201,12 +5201,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>59,53%</t>
+          <t>60,33%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>80,88%</t>
+          <t>81,58%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5221,12 +5221,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>37909</t>
+          <t>38008</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>50079</t>
+          <t>50141</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5236,12 +5236,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>61,19%</t>
+          <t>61,35%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>80,83%</t>
+          <t>80,93%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5256,12 +5256,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>72992</t>
+          <t>73817</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>89959</t>
+          <t>90179</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5271,12 +5271,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>63,47%</t>
+          <t>64,19%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>78,22%</t>
+          <t>78,41%</t>
         </is>
       </c>
     </row>
@@ -5299,12 +5299,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7911</t>
+          <t>7708</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>18565</t>
+          <t>18593</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5314,12 +5314,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>35,0%</t>
+          <t>35,05%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5334,12 +5334,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>6660</t>
+          <t>6090</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>17011</t>
+          <t>17131</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5349,12 +5349,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>27,46%</t>
+          <t>27,65%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>16490</t>
+          <t>16876</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>31448</t>
+          <t>32517</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5384,12 +5384,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>27,35%</t>
+          <t>28,27%</t>
         </is>
       </c>
     </row>
@@ -5529,12 +5529,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1620</t>
+          <t>1687</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>8334</t>
+          <t>9124</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5544,12 +5544,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5564,12 +5564,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1925</t>
+          <t>2060</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>9414</t>
+          <t>9253</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5579,12 +5579,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5599,12 +5599,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4875</t>
+          <t>4849</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>14784</t>
+          <t>15313</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5614,12 +5614,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,92%</t>
         </is>
       </c>
     </row>
@@ -5642,12 +5642,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>73328</t>
+          <t>73711</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>85422</t>
+          <t>85787</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5657,12 +5657,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>76,96%</t>
+          <t>77,36%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>89,65%</t>
+          <t>90,03%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5677,12 +5677,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>78241</t>
+          <t>77925</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>89364</t>
+          <t>89235</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5692,12 +5692,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>79,73%</t>
+          <t>79,41%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>91,06%</t>
+          <t>90,93%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5712,12 +5712,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>155005</t>
+          <t>154942</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>171366</t>
+          <t>171828</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5727,12 +5727,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>80,14%</t>
+          <t>80,11%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>88,6%</t>
+          <t>88,84%</t>
         </is>
       </c>
     </row>
@@ -5755,12 +5755,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6332</t>
+          <t>6271</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16867</t>
+          <t>16488</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5770,12 +5770,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>17,3%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5790,12 +5790,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5118</t>
+          <t>5166</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14675</t>
+          <t>14588</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5825,12 +5825,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>13899</t>
+          <t>14051</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>28017</t>
+          <t>28666</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>14,82%</t>
         </is>
       </c>
     </row>
@@ -5985,12 +5985,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1563</t>
+          <t>1466</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8647</t>
+          <t>8491</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6000,12 +6000,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6020,12 +6020,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2716</t>
+          <t>2238</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>10492</t>
+          <t>10186</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6035,12 +6035,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6055,12 +6055,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>5407</t>
+          <t>5471</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>15638</t>
+          <t>15193</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6070,12 +6070,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>10,96%</t>
         </is>
       </c>
     </row>
@@ -6098,12 +6098,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>47380</t>
+          <t>47386</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>58617</t>
+          <t>58401</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6113,12 +6113,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>70,28%</t>
+          <t>70,29%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>86,95%</t>
+          <t>86,63%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6133,12 +6133,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>44081</t>
+          <t>44562</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>56330</t>
+          <t>56896</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>61,86%</t>
+          <t>62,54%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>79,05%</t>
+          <t>79,85%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6168,12 +6168,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>95047</t>
+          <t>94955</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>111698</t>
+          <t>112046</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>68,54%</t>
+          <t>68,48%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>80,55%</t>
+          <t>80,8%</t>
         </is>
       </c>
     </row>
@@ -6211,12 +6211,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5657</t>
+          <t>5859</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>15664</t>
+          <t>15871</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>23,24%</t>
+          <t>23,54%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6246,12 +6246,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>9836</t>
+          <t>9988</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>21493</t>
+          <t>21210</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>30,16%</t>
+          <t>29,77%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6281,12 +6281,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>18371</t>
+          <t>17371</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>33568</t>
+          <t>32450</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>24,21%</t>
+          <t>23,4%</t>
         </is>
       </c>
     </row>
@@ -6441,12 +6441,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>625</t>
+          <t>647</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5841</t>
+          <t>6046</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>662</t>
+          <t>666</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7159</t>
+          <t>6189</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6496,7 +6496,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6511,12 +6511,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1944</t>
+          <t>1668</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>9783</t>
+          <t>9445</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6526,12 +6526,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,23%</t>
         </is>
       </c>
     </row>
@@ -6554,12 +6554,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>57760</t>
+          <t>58225</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>67196</t>
+          <t>67618</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6569,12 +6569,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>79,85%</t>
+          <t>80,49%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>92,9%</t>
+          <t>93,48%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>66668</t>
+          <t>67418</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>75574</t>
+          <t>75687</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6604,12 +6604,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>84,15%</t>
+          <t>85,09%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>95,53%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>128280</t>
+          <t>128159</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>140812</t>
+          <t>141048</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6639,12 +6639,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>84,64%</t>
+          <t>84,56%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,91%</t>
+          <t>93,06%</t>
         </is>
       </c>
     </row>
@@ -6667,12 +6667,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3445</t>
+          <t>3151</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>11927</t>
+          <t>11459</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6682,12 +6682,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2050</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>9282</t>
+          <t>9540</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6717,12 +6717,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>6806</t>
+          <t>7057</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>17564</t>
+          <t>18642</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6752,12 +6752,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>12,3%</t>
         </is>
       </c>
     </row>
@@ -6937,7 +6937,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>4782</t>
+          <t>4010</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6952,7 +6952,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6972,7 +6972,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>4088</t>
+          <t>4609</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6987,7 +6987,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>5,57%</t>
         </is>
       </c>
     </row>
@@ -7010,12 +7010,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>21123</t>
+          <t>20786</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>30920</t>
+          <t>30947</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7025,12 +7025,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>53,44%</t>
+          <t>52,59%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>78,23%</t>
+          <t>78,3%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>21451</t>
+          <t>21239</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>32368</t>
+          <t>31704</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7060,12 +7060,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>49,57%</t>
+          <t>49,07%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>74,79%</t>
+          <t>73,26%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>45542</t>
+          <t>45887</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>60672</t>
+          <t>60192</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7095,12 +7095,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>55,0%</t>
+          <t>55,42%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>73,27%</t>
+          <t>72,69%</t>
         </is>
       </c>
     </row>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>8604</t>
+          <t>8577</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>18401</t>
+          <t>18738</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>21,7%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>46,56%</t>
+          <t>47,41%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7158,12 +7158,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>9931</t>
+          <t>10157</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>20072</t>
+          <t>20963</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>23,47%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>46,38%</t>
+          <t>48,44%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7193,12 +7193,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>20815</t>
+          <t>21648</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>35981</t>
+          <t>36050</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7208,12 +7208,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>25,14%</t>
+          <t>26,14%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>43,45%</t>
+          <t>43,54%</t>
         </is>
       </c>
     </row>
@@ -7353,12 +7353,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2271</t>
+          <t>2262</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>9806</t>
+          <t>10071</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -7368,12 +7368,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>18,22%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2237</t>
+          <t>2417</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>9232</t>
+          <t>9291</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -7403,12 +7403,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>15,73%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6516</t>
+          <t>6380</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>15747</t>
+          <t>16776</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -7438,12 +7438,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>14,67%</t>
         </is>
       </c>
     </row>
@@ -7466,12 +7466,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>32394</t>
+          <t>32452</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>44286</t>
+          <t>44127</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7481,12 +7481,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>58,62%</t>
+          <t>58,73%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>80,14%</t>
+          <t>79,85%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7501,12 +7501,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>34845</t>
+          <t>35953</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>47035</t>
+          <t>47203</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7516,12 +7516,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>58,98%</t>
+          <t>60,85%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>79,61%</t>
+          <t>79,9%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7536,12 +7536,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>72569</t>
+          <t>72637</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>88363</t>
+          <t>89076</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7551,12 +7551,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>63,47%</t>
+          <t>63,53%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>77,28%</t>
+          <t>77,9%</t>
         </is>
       </c>
     </row>
@@ -7579,12 +7579,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>6625</t>
+          <t>6631</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>15962</t>
+          <t>16793</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7594,12 +7594,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>28,89%</t>
+          <t>30,39%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7614,12 +7614,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>7430</t>
+          <t>7773</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>17772</t>
+          <t>17732</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7629,12 +7629,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>30,08%</t>
+          <t>30,01%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7649,12 +7649,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>16457</t>
+          <t>16276</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>30499</t>
+          <t>30502</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7664,12 +7664,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>14,23%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>26,67%</t>
+          <t>26,68%</t>
         </is>
       </c>
     </row>
@@ -7809,12 +7809,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>4906</t>
+          <t>4875</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>14812</t>
+          <t>14498</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7824,12 +7824,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7844,12 +7844,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>7015</t>
+          <t>6786</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>18726</t>
+          <t>18929</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7859,12 +7859,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7879,12 +7879,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>14169</t>
+          <t>13945</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>28996</t>
+          <t>28344</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7894,12 +7894,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,17%</t>
         </is>
       </c>
     </row>
@@ -7922,12 +7922,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>94542</t>
+          <t>94659</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>111248</t>
+          <t>111069</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7937,12 +7937,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>70,02%</t>
+          <t>70,11%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>82,39%</t>
+          <t>82,26%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7957,12 +7957,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>100469</t>
+          <t>99733</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>116500</t>
+          <t>116905</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7972,12 +7972,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>69,89%</t>
+          <t>69,38%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>81,04%</t>
+          <t>81,32%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7992,12 +7992,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>198834</t>
+          <t>198850</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>222556</t>
+          <t>223799</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8012,7 +8012,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>79,83%</t>
+          <t>80,28%</t>
         </is>
       </c>
     </row>
@@ -8035,12 +8035,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>15333</t>
+          <t>15438</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>29726</t>
+          <t>29962</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8050,12 +8050,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>22,19%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8070,12 +8070,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>16916</t>
+          <t>16570</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>31250</t>
+          <t>31247</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8085,7 +8085,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -8105,12 +8105,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>36968</t>
+          <t>36291</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>57560</t>
+          <t>58564</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8120,12 +8120,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>20,65%</t>
+          <t>21,01%</t>
         </is>
       </c>
     </row>
@@ -8265,12 +8265,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>3490</t>
+          <t>3267</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>12004</t>
+          <t>12025</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8280,12 +8280,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8300,12 +8300,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>8983</t>
+          <t>8877</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>20398</t>
+          <t>20754</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8315,12 +8315,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8335,12 +8335,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>14088</t>
+          <t>13901</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>28244</t>
+          <t>28436</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -8350,12 +8350,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>9,07%</t>
         </is>
       </c>
     </row>
@@ -8378,12 +8378,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>114732</t>
+          <t>114975</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>130417</t>
+          <t>130003</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -8393,12 +8393,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>75,12%</t>
+          <t>75,28%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>85,39%</t>
+          <t>85,12%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -8413,12 +8413,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>117113</t>
+          <t>117904</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>134378</t>
+          <t>134963</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -8428,12 +8428,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>72,82%</t>
+          <t>73,31%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>83,56%</t>
+          <t>83,92%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -8448,12 +8448,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>237747</t>
+          <t>238399</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>261141</t>
+          <t>260904</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -8463,12 +8463,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>75,82%</t>
+          <t>76,03%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>83,29%</t>
+          <t>83,21%</t>
         </is>
       </c>
     </row>
@@ -8491,12 +8491,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>16706</t>
+          <t>16852</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>30685</t>
+          <t>30579</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8506,12 +8506,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8526,12 +8526,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>14244</t>
+          <t>14040</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>28361</t>
+          <t>28094</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8541,12 +8541,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8561,12 +8561,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>34244</t>
+          <t>33890</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>53413</t>
+          <t>53826</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8576,12 +8576,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>17,17%</t>
         </is>
       </c>
     </row>
@@ -8721,12 +8721,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>26031</t>
+          <t>26679</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>44964</t>
+          <t>45399</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -8736,12 +8736,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -8756,12 +8756,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>40346</t>
+          <t>39674</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>62412</t>
+          <t>62672</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -8771,12 +8771,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -8791,12 +8791,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>71474</t>
+          <t>71668</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>100599</t>
+          <t>100686</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -8806,7 +8806,7 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>507738</t>
+          <t>510554</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>543449</t>
+          <t>545942</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -8849,12 +8849,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>75,71%</t>
+          <t>76,13%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>81,04%</t>
+          <t>81,41%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -8869,12 +8869,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>535959</t>
+          <t>534989</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>574154</t>
+          <t>573493</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -8884,12 +8884,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>74,7%</t>
+          <t>74,56%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>80,02%</t>
+          <t>79,93%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -8904,12 +8904,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>1057224</t>
+          <t>1056504</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>1108670</t>
+          <t>1106926</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -8919,12 +8919,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>76,16%</t>
+          <t>76,11%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>79,87%</t>
+          <t>79,74%</t>
         </is>
       </c>
     </row>
@@ -8947,12 +8947,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>92957</t>
+          <t>92977</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>126240</t>
+          <t>125513</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -8967,7 +8967,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -8982,12 +8982,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>96195</t>
+          <t>95324</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>126511</t>
+          <t>129567</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -8997,12 +8997,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>18,06%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -9017,12 +9017,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>196712</t>
+          <t>200046</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>241298</t>
+          <t>244351</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -9032,12 +9032,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>17,6%</t>
         </is>
       </c>
     </row>
@@ -9413,12 +9413,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2428</t>
+          <t>2468</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10260</t>
+          <t>10851</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9428,12 +9428,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>19,93%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9448,12 +9448,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>593</t>
+          <t>565</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5959</t>
+          <t>5282</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9463,12 +9463,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4032</t>
+          <t>3832</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>13559</t>
+          <t>13454</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9498,12 +9498,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>11,89%</t>
         </is>
       </c>
     </row>
@@ -9526,12 +9526,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>33851</t>
+          <t>33670</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>44183</t>
+          <t>44338</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9541,12 +9541,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>62,18%</t>
+          <t>61,85%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>81,16%</t>
+          <t>81,44%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9561,12 +9561,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>40315</t>
+          <t>39576</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>51203</t>
+          <t>50743</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9576,12 +9576,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>68,68%</t>
+          <t>67,42%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>87,23%</t>
+          <t>86,45%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9596,12 +9596,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>77401</t>
+          <t>76813</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>92538</t>
+          <t>92090</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9611,12 +9611,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>68,41%</t>
+          <t>67,89%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>81,79%</t>
+          <t>81,4%</t>
         </is>
       </c>
     </row>
@@ -9639,12 +9639,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6058</t>
+          <t>6146</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>14623</t>
+          <t>15223</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9654,12 +9654,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>26,86%</t>
+          <t>27,96%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9674,12 +9674,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5656</t>
+          <t>5575</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>15950</t>
+          <t>16059</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9689,12 +9689,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>27,17%</t>
+          <t>27,36%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9709,12 +9709,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>14037</t>
+          <t>14087</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>27465</t>
+          <t>28150</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -9724,12 +9724,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>24,88%</t>
         </is>
       </c>
     </row>
@@ -9869,12 +9869,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2466</t>
+          <t>2550</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>9823</t>
+          <t>10316</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9884,12 +9884,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9904,12 +9904,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>5272</t>
+          <t>4735</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>15384</t>
+          <t>14691</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9919,12 +9919,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>15,55%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9939,12 +9939,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>9128</t>
+          <t>9273</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>21229</t>
+          <t>21589</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9954,12 +9954,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,68%</t>
         </is>
       </c>
     </row>
@@ -9982,12 +9982,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>59668</t>
+          <t>59826</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>72937</t>
+          <t>73649</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9997,12 +9997,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>66,06%</t>
+          <t>66,24%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>80,76%</t>
+          <t>81,54%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -10017,12 +10017,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>60159</t>
+          <t>58687</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>74267</t>
+          <t>73843</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10032,12 +10032,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>63,68%</t>
+          <t>62,12%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>78,61%</t>
+          <t>78,17%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -10052,12 +10052,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>123367</t>
+          <t>124173</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>143692</t>
+          <t>144589</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10067,12 +10067,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>66,76%</t>
+          <t>67,2%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>77,76%</t>
+          <t>78,25%</t>
         </is>
       </c>
     </row>
@@ -10095,12 +10095,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11824</t>
+          <t>11910</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>24985</t>
+          <t>24762</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10110,12 +10110,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>27,66%</t>
+          <t>27,42%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10130,12 +10130,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>12610</t>
+          <t>12501</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>25011</t>
+          <t>25309</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10145,12 +10145,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>26,47%</t>
+          <t>26,79%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10165,12 +10165,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>27508</t>
+          <t>27034</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>46415</t>
+          <t>45870</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10180,12 +10180,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>25,12%</t>
+          <t>24,82%</t>
         </is>
       </c>
     </row>
@@ -10330,7 +10330,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5170</t>
+          <t>5060</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10345,7 +10345,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10360,12 +10360,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>660</t>
+          <t>662</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5558</t>
+          <t>5456</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10380,7 +10380,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10395,12 +10395,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1360</t>
+          <t>1344</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>7788</t>
+          <t>7708</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10410,12 +10410,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>5,98%</t>
         </is>
       </c>
     </row>
@@ -10438,12 +10438,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>45137</t>
+          <t>45376</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>57095</t>
+          <t>56990</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10453,12 +10453,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>68,32%</t>
+          <t>68,68%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>86,42%</t>
+          <t>86,26%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10473,12 +10473,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>46222</t>
+          <t>46270</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>56176</t>
+          <t>56168</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10488,12 +10488,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>73,6%</t>
+          <t>73,68%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>89,45%</t>
+          <t>89,44%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10508,12 +10508,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>95139</t>
+          <t>95507</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>110068</t>
+          <t>110601</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10523,12 +10523,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>73,83%</t>
+          <t>74,11%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>85,41%</t>
+          <t>85,83%</t>
         </is>
       </c>
     </row>
@@ -10551,12 +10551,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>8151</t>
+          <t>8005</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>19735</t>
+          <t>19321</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10566,12 +10566,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>29,87%</t>
+          <t>29,24%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10586,12 +10586,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>5133</t>
+          <t>5194</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>14832</t>
+          <t>14456</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10601,12 +10601,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>23,62%</t>
+          <t>23,02%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10621,12 +10621,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>15686</t>
+          <t>15211</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>30590</t>
+          <t>30264</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10636,12 +10636,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>23,49%</t>
         </is>
       </c>
     </row>
@@ -10786,7 +10786,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4961</t>
+          <t>4359</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10801,7 +10801,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10816,12 +10816,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3686</t>
+          <t>3396</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>13005</t>
+          <t>12981</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10831,12 +10831,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10851,12 +10851,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4622</t>
+          <t>4351</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>15710</t>
+          <t>14432</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10866,12 +10866,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>9,51%</t>
         </is>
       </c>
     </row>
@@ -10894,12 +10894,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>62451</t>
+          <t>62326</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>71021</t>
+          <t>70622</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10909,12 +10909,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>85,24%</t>
+          <t>85,07%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>96,4%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10929,12 +10929,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>53824</t>
+          <t>54671</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>67098</t>
+          <t>67165</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10944,12 +10944,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>68,57%</t>
+          <t>69,65%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>85,49%</t>
+          <t>85,57%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10964,12 +10964,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>120003</t>
+          <t>119654</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>136590</t>
+          <t>136084</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10979,12 +10979,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>79,08%</t>
+          <t>78,85%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>90,01%</t>
+          <t>89,67%</t>
         </is>
       </c>
     </row>
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1413</t>
+          <t>1703</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>9178</t>
+          <t>8643</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11022,12 +11022,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -11042,12 +11042,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>5765</t>
+          <t>5658</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>16454</t>
+          <t>16199</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11057,12 +11057,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>20,64%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -11077,12 +11077,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>9103</t>
+          <t>9033</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>22368</t>
+          <t>21788</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>14,36%</t>
         </is>
       </c>
     </row>
@@ -11237,12 +11237,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>775</t>
+          <t>753</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>6974</t>
+          <t>6539</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11252,12 +11252,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>15,64%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11272,12 +11272,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>659</t>
+          <t>654</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>6287</t>
+          <t>5794</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11287,12 +11287,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11307,12 +11307,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2097</t>
+          <t>2091</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>9219</t>
+          <t>9519</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11322,12 +11322,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,98%</t>
         </is>
       </c>
     </row>
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>30840</t>
+          <t>30980</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>38670</t>
+          <t>38759</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11365,12 +11365,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>73,76%</t>
+          <t>74,1%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>92,49%</t>
+          <t>92,71%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -11385,12 +11385,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>30506</t>
+          <t>31068</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>39924</t>
+          <t>40175</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11400,12 +11400,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>67,97%</t>
+          <t>69,22%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>88,95%</t>
+          <t>89,51%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -11420,12 +11420,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>65583</t>
+          <t>65830</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>76737</t>
+          <t>77187</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11435,12 +11435,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>75,65%</t>
+          <t>75,94%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>88,52%</t>
+          <t>89,04%</t>
         </is>
       </c>
     </row>
@@ -11463,12 +11463,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1266</t>
+          <t>1286</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>7265</t>
+          <t>7609</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11478,12 +11478,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11498,12 +11498,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3516</t>
+          <t>3171</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>11899</t>
+          <t>11480</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11513,12 +11513,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>26,51%</t>
+          <t>25,58%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11533,12 +11533,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>5969</t>
+          <t>5675</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>15621</t>
+          <t>15789</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11548,12 +11548,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>18,02%</t>
+          <t>18,21%</t>
         </is>
       </c>
     </row>
@@ -11693,12 +11693,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>646</t>
+          <t>631</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>6418</t>
+          <t>6163</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11708,12 +11708,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11728,12 +11728,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3024</t>
+          <t>3147</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>11539</t>
+          <t>11708</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -11743,12 +11743,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>20,53%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>4633</t>
+          <t>4652</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>14644</t>
+          <t>14775</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -11778,12 +11778,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>13,62%</t>
         </is>
       </c>
     </row>
@@ -11806,12 +11806,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>11563</t>
+          <t>11525</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>22304</t>
+          <t>22544</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -11821,12 +11821,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>22,39%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>43,32%</t>
+          <t>43,79%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -11841,12 +11841,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>13568</t>
+          <t>14485</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>26873</t>
+          <t>26404</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -11856,12 +11856,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>23,79%</t>
+          <t>25,4%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>47,13%</t>
+          <t>46,3%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -11876,12 +11876,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>28960</t>
+          <t>28723</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>46129</t>
+          <t>44850</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -11891,12 +11891,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>26,69%</t>
+          <t>26,47%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>42,51%</t>
+          <t>41,33%</t>
         </is>
       </c>
     </row>
@@ -11919,12 +11919,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>26725</t>
+          <t>26856</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>37579</t>
+          <t>37688</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -11934,12 +11934,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>51,91%</t>
+          <t>52,16%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>72,99%</t>
+          <t>73,21%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -11954,12 +11954,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>23865</t>
+          <t>24050</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>36974</t>
+          <t>37032</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -11969,12 +11969,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>41,85%</t>
+          <t>42,18%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>64,84%</t>
+          <t>64,94%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -11989,12 +11989,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>53358</t>
+          <t>53907</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>71460</t>
+          <t>71390</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12004,12 +12004,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>49,18%</t>
+          <t>49,68%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>65,86%</t>
+          <t>65,79%</t>
         </is>
       </c>
     </row>
@@ -12149,12 +12149,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1264</t>
+          <t>1759</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>8026</t>
+          <t>7442</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -12164,12 +12164,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -12189,7 +12189,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>8031</t>
+          <t>7155</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -12204,7 +12204,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3591</t>
+          <t>3354</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>12167</t>
+          <t>13262</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,89%</t>
         </is>
       </c>
     </row>
@@ -12262,12 +12262,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>60437</t>
+          <t>60949</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>77178</t>
+          <t>76963</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -12277,12 +12277,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>54,18%</t>
+          <t>54,64%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>69,19%</t>
+          <t>69,0%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -12297,12 +12297,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>66020</t>
+          <t>66336</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>82949</t>
+          <t>83095</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -12312,12 +12312,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>58,16%</t>
+          <t>58,44%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>73,08%</t>
+          <t>73,2%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -12332,12 +12332,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>131958</t>
+          <t>132511</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>154480</t>
+          <t>155257</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -12347,12 +12347,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>58,63%</t>
+          <t>58,88%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>68,64%</t>
+          <t>68,99%</t>
         </is>
       </c>
     </row>
@@ -12375,12 +12375,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>31019</t>
+          <t>30984</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>47355</t>
+          <t>46808</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -12390,12 +12390,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>27,81%</t>
+          <t>27,78%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>42,45%</t>
+          <t>41,96%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -12410,12 +12410,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>27432</t>
+          <t>27704</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>44116</t>
+          <t>44162</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -12425,12 +12425,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>24,17%</t>
+          <t>24,41%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>38,86%</t>
+          <t>38,91%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -12445,12 +12445,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>63571</t>
+          <t>63259</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>85796</t>
+          <t>85077</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -12460,12 +12460,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>28,25%</t>
+          <t>28,11%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>38,12%</t>
+          <t>37,8%</t>
         </is>
       </c>
     </row>
@@ -12605,12 +12605,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>3343</t>
+          <t>3891</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>12151</t>
+          <t>12309</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -12620,12 +12620,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>4293</t>
+          <t>4617</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>14160</t>
+          <t>13987</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -12655,12 +12655,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -12675,12 +12675,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>9820</t>
+          <t>10010</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>23086</t>
+          <t>22079</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -12690,12 +12690,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>6,78%</t>
         </is>
       </c>
     </row>
@@ -12718,12 +12718,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>128051</t>
+          <t>127156</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>142665</t>
+          <t>142461</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -12733,12 +12733,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>80,15%</t>
+          <t>79,59%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>89,3%</t>
+          <t>89,17%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -12753,12 +12753,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>128174</t>
+          <t>129250</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>144283</t>
+          <t>144423</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -12768,12 +12768,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>77,34%</t>
+          <t>77,99%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>87,06%</t>
+          <t>87,14%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -12788,12 +12788,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>261936</t>
+          <t>263131</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>282654</t>
+          <t>284833</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -12803,12 +12803,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>80,47%</t>
+          <t>80,84%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>86,84%</t>
+          <t>87,51%</t>
         </is>
       </c>
     </row>
@@ -12831,12 +12831,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>11354</t>
+          <t>11299</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>23830</t>
+          <t>24583</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -12846,12 +12846,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>15,39%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -12866,12 +12866,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>13876</t>
+          <t>13611</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>27702</t>
+          <t>27184</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -12881,12 +12881,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -12901,12 +12901,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>28570</t>
+          <t>27036</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>46697</t>
+          <t>46229</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -12916,12 +12916,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>14,2%</t>
         </is>
       </c>
     </row>
@@ -13061,12 +13061,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>21205</t>
+          <t>22215</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>39404</t>
+          <t>39758</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -13076,12 +13076,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -13096,12 +13096,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>30280</t>
+          <t>31493</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>52061</t>
+          <t>53121</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -13111,12 +13111,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -13131,12 +13131,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>57203</t>
+          <t>57679</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>84244</t>
+          <t>84218</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -13146,7 +13146,7 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>463851</t>
+          <t>463582</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>501824</t>
+          <t>499803</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -13189,12 +13189,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>71,51%</t>
+          <t>71,46%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>77,36%</t>
+          <t>77,05%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -13209,12 +13209,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>476442</t>
+          <t>475281</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>514206</t>
+          <t>514934</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -13224,12 +13224,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>70,52%</t>
+          <t>70,35%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>76,11%</t>
+          <t>76,22%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -13244,12 +13244,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>948962</t>
+          <t>952048</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>1004038</t>
+          <t>1003988</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -13259,12 +13259,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>71,66%</t>
+          <t>71,89%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>75,82%</t>
+          <t>75,81%</t>
         </is>
       </c>
     </row>
@@ -13287,12 +13287,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>118194</t>
+          <t>119075</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>153281</t>
+          <t>152959</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -13302,12 +13302,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>18,36%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>23,63%</t>
+          <t>23,58%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -13322,12 +13322,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>121365</t>
+          <t>122331</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>157614</t>
+          <t>158757</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -13337,12 +13337,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>18,11%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>23,5%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -13357,12 +13357,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>251289</t>
+          <t>251407</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>300680</t>
+          <t>299076</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -13377,7 +13377,7 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>22,58%</t>
         </is>
       </c>
     </row>
@@ -13753,12 +13753,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>595</t>
+          <t>597</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5483</t>
+          <t>5185</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -13768,12 +13768,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>45,35%</t>
+          <t>42,88%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -13793,7 +13793,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3745</t>
+          <t>3627</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -13808,7 +13808,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>26,63%</t>
+          <t>25,79%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -13823,12 +13823,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1286</t>
+          <t>1076</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7049</t>
+          <t>7021</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -13838,12 +13838,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>26,95%</t>
+          <t>26,84%</t>
         </is>
       </c>
     </row>
@@ -13866,12 +13866,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6608</t>
+          <t>6906</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11496</t>
+          <t>11494</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -13881,12 +13881,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>54,65%</t>
+          <t>57,12%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>95,06%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -13901,12 +13901,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6997</t>
+          <t>6746</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>12778</t>
+          <t>12788</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -13916,12 +13916,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>49,75%</t>
+          <t>47,96%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>90,86%</t>
+          <t>90,92%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -13936,12 +13936,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>15831</t>
+          <t>15904</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>23389</t>
+          <t>23256</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -13951,12 +13951,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>60,53%</t>
+          <t>60,81%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>89,42%</t>
+          <t>88,91%</t>
         </is>
       </c>
     </row>
@@ -14014,12 +14014,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>636</t>
+          <t>623</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6890</t>
+          <t>6677</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -14029,12 +14029,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>48,99%</t>
+          <t>47,48%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -14049,12 +14049,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>646</t>
+          <t>641</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>7338</t>
+          <t>7505</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -14064,12 +14064,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>28,05%</t>
+          <t>28,69%</t>
         </is>
       </c>
     </row>
@@ -14214,7 +14214,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3782</t>
+          <t>3391</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -14229,7 +14229,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>27,75%</t>
+          <t>24,88%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -14284,7 +14284,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3617</t>
+          <t>3382</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -14299,7 +14299,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>11,29%</t>
         </is>
       </c>
     </row>
@@ -14322,7 +14322,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9847</t>
+          <t>10238</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -14337,7 +14337,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>72,25%</t>
+          <t>75,12%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -14357,7 +14357,7 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>10883</t>
+          <t>10876</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -14372,7 +14372,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>66,65%</t>
+          <t>66,6%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -14392,12 +14392,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>22635</t>
+          <t>22372</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>29118</t>
+          <t>29168</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -14407,12 +14407,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>75,55%</t>
+          <t>74,68%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,36%</t>
         </is>
       </c>
     </row>
@@ -14475,7 +14475,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5447</t>
+          <t>5454</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -14490,7 +14490,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>33,35%</t>
+          <t>33,4%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -14510,7 +14510,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5919</t>
+          <t>6431</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -14525,7 +14525,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>21,47%</t>
         </is>
       </c>
     </row>
@@ -14665,12 +14665,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>587</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4592</t>
+          <t>4609</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -14685,7 +14685,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>32,9%</t>
+          <t>33,02%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -14700,12 +14700,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>687</t>
+          <t>713</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>6057</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -14715,12 +14715,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>32,56%</t>
+          <t>36,88%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -14735,12 +14735,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1431</t>
+          <t>1724</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>7982</t>
+          <t>8083</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>26,28%</t>
+          <t>26,61%</t>
         </is>
       </c>
     </row>
@@ -14778,12 +14778,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4773</t>
+          <t>4615</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10392</t>
+          <t>10342</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -14793,12 +14793,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>34,2%</t>
+          <t>33,06%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>74,45%</t>
+          <t>74,1%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -14813,12 +14813,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9678</t>
+          <t>9284</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>15250</t>
+          <t>15155</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -14828,12 +14828,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>58,93%</t>
+          <t>56,54%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>92,86%</t>
+          <t>92,29%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -14848,12 +14848,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>15652</t>
+          <t>15952</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>24223</t>
+          <t>24010</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -14863,12 +14863,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>51,52%</t>
+          <t>52,51%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>79,74%</t>
+          <t>79,03%</t>
         </is>
       </c>
     </row>
@@ -14891,12 +14891,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2197</t>
+          <t>2387</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>7323</t>
+          <t>7940</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -14906,12 +14906,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>15,74%</t>
+          <t>17,11%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>52,47%</t>
+          <t>56,89%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -14931,7 +14931,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3991</t>
+          <t>3878</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -14946,7 +14946,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>24,3%</t>
+          <t>23,61%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -14961,12 +14961,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3195</t>
+          <t>3169</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>9791</t>
+          <t>10204</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -14976,12 +14976,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>32,23%</t>
+          <t>33,59%</t>
         </is>
       </c>
     </row>
@@ -15121,12 +15121,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>169</t>
+          <t>151</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6636</t>
+          <t>5462</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -15136,12 +15136,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>50,02%</t>
+          <t>41,17%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -15161,7 +15161,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5840</t>
+          <t>5525</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -15176,7 +15176,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>39,74%</t>
+          <t>37,6%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -15191,12 +15191,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1335</t>
+          <t>1157</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>9361</t>
+          <t>8721</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -15206,12 +15206,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>33,48%</t>
+          <t>31,19%</t>
         </is>
       </c>
     </row>
@@ -15234,12 +15234,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4817</t>
+          <t>5148</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>11329</t>
+          <t>11782</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -15249,12 +15249,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>36,31%</t>
+          <t>38,8%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>85,38%</t>
+          <t>88,8%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -15269,12 +15269,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5090</t>
+          <t>4683</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>13470</t>
+          <t>13516</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -15284,12 +15284,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>34,64%</t>
+          <t>31,87%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,67%</t>
+          <t>91,98%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -15304,12 +15304,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>12876</t>
+          <t>12818</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>23165</t>
+          <t>23178</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -15319,12 +15319,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>46,05%</t>
+          <t>45,84%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>82,84%</t>
+          <t>82,89%</t>
         </is>
       </c>
     </row>
@@ -15347,12 +15347,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>546</t>
+          <t>607</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>6483</t>
+          <t>6044</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -15362,12 +15362,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>48,86%</t>
+          <t>45,55%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -15387,7 +15387,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>9384</t>
+          <t>9010</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -15402,7 +15402,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>63,86%</t>
+          <t>61,32%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -15417,12 +15417,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1893</t>
+          <t>1881</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>12996</t>
+          <t>12096</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -15432,12 +15432,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>46,48%</t>
+          <t>43,26%</t>
         </is>
       </c>
     </row>
@@ -15725,12 +15725,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1395</t>
+          <t>1418</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>4734</t>
+          <t>4746</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -15740,12 +15740,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>26,04%</t>
+          <t>26,47%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>88,37%</t>
+          <t>88,6%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -15760,12 +15760,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>4802</t>
+          <t>4807</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>9324</t>
+          <t>8744</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -15775,12 +15775,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>51,5%</t>
+          <t>51,56%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>93,78%</t>
         </is>
       </c>
     </row>
@@ -15838,12 +15838,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>623</t>
+          <t>611</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3961</t>
+          <t>3944</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -15853,12 +15853,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>73,93%</t>
+          <t>73,63%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -15873,12 +15873,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>580</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4522</t>
+          <t>4517</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -15888,12 +15888,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>48,5%</t>
+          <t>48,44%</t>
         </is>
       </c>
     </row>
@@ -16033,12 +16033,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>464</t>
+          <t>465</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3771</t>
+          <t>3901</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -16048,12 +16048,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>41,29%</t>
+          <t>42,71%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -16068,12 +16068,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>545</t>
+          <t>568</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>5062</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -16083,12 +16083,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>29,68%</t>
+          <t>29,2%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1241</t>
+          <t>1559</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>7036</t>
+          <t>7222</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -16118,12 +16118,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>26,87%</t>
+          <t>27,58%</t>
         </is>
       </c>
     </row>
@@ -16146,12 +16146,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3618</t>
+          <t>3964</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>8016</t>
+          <t>8099</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -16161,12 +16161,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>39,62%</t>
+          <t>43,4%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>87,77%</t>
+          <t>88,68%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -16181,12 +16181,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>9420</t>
+          <t>9548</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>15075</t>
+          <t>15084</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -16196,12 +16196,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>55,24%</t>
+          <t>55,98%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>88,39%</t>
+          <t>88,44%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -16216,12 +16216,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>14982</t>
+          <t>14858</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>22217</t>
+          <t>21775</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -16231,12 +16231,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>57,21%</t>
+          <t>56,74%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>84,84%</t>
+          <t>83,15%</t>
         </is>
       </c>
     </row>
@@ -16264,7 +16264,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3843</t>
+          <t>4020</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -16279,7 +16279,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>42,08%</t>
+          <t>44,02%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -16294,12 +16294,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>782</t>
+          <t>788</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>5491</t>
+          <t>5915</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -16309,12 +16309,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>32,2%</t>
+          <t>34,68%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -16329,12 +16329,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1544</t>
+          <t>1619</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>7539</t>
+          <t>7457</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -16344,12 +16344,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>28,79%</t>
+          <t>28,47%</t>
         </is>
       </c>
     </row>
@@ -16489,12 +16489,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>754</t>
+          <t>728</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>6605</t>
+          <t>6304</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -16504,12 +16504,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>29,63%</t>
+          <t>28,28%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -16524,12 +16524,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1581</t>
+          <t>1684</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>8773</t>
+          <t>8685</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -16539,12 +16539,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>31,64%</t>
+          <t>31,32%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -16559,12 +16559,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3423</t>
+          <t>3332</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>12530</t>
+          <t>11940</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -16574,12 +16574,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>25,05%</t>
+          <t>23,87%</t>
         </is>
       </c>
     </row>
@@ -16602,12 +16602,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>14287</t>
+          <t>15047</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>20849</t>
+          <t>20979</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -16617,12 +16617,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>64,1%</t>
+          <t>67,5%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>93,53%</t>
+          <t>94,11%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -16637,12 +16637,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>11380</t>
+          <t>11166</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>20661</t>
+          <t>20420</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -16652,12 +16652,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>41,05%</t>
+          <t>40,27%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>74,52%</t>
+          <t>73,65%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -16672,12 +16672,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>28044</t>
+          <t>28444</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>40219</t>
+          <t>40737</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -16687,12 +16687,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>56,07%</t>
+          <t>56,87%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>80,41%</t>
+          <t>81,45%</t>
         </is>
       </c>
     </row>
@@ -16720,7 +16720,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3489</t>
+          <t>4480</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -16735,7 +16735,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>20,1%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -16750,12 +16750,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3557</t>
+          <t>3593</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>11929</t>
+          <t>12386</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -16765,12 +16765,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>43,02%</t>
+          <t>44,67%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -16785,12 +16785,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>4137</t>
+          <t>4115</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>14826</t>
+          <t>14675</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -16800,12 +16800,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>29,64%</t>
+          <t>29,34%</t>
         </is>
       </c>
     </row>
@@ -16980,12 +16980,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>357</t>
+          <t>353</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>5759</t>
+          <t>6033</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -16995,12 +16995,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>28,88%</t>
+          <t>30,25%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -17015,12 +17015,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>361</t>
+          <t>379</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>5874</t>
+          <t>5761</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -17030,12 +17030,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>18,05%</t>
         </is>
       </c>
     </row>
@@ -17058,7 +17058,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>7719</t>
+          <t>7973</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -17073,7 +17073,7 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>64,44%</t>
+          <t>66,56%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
@@ -17093,12 +17093,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>12119</t>
+          <t>11811</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>18271</t>
+          <t>18288</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -17108,12 +17108,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>60,77%</t>
+          <t>59,22%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>91,62%</t>
+          <t>91,71%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -17128,12 +17128,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>21856</t>
+          <t>21608</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>29533</t>
+          <t>29451</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -17143,12 +17143,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>68,47%</t>
+          <t>67,69%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>92,52%</t>
+          <t>92,27%</t>
         </is>
       </c>
     </row>
@@ -17176,7 +17176,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>4259</t>
+          <t>4005</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -17191,7 +17191,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>35,56%</t>
+          <t>33,44%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -17206,12 +17206,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>660</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>5473</t>
+          <t>5280</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -17221,12 +17221,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>27,44%</t>
+          <t>26,48%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -17241,12 +17241,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>738</t>
+          <t>768</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>7287</t>
+          <t>7603</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -17256,12 +17256,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>23,82%</t>
         </is>
       </c>
     </row>
@@ -17401,12 +17401,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>7095</t>
+          <t>7330</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>17965</t>
+          <t>18001</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -17416,12 +17416,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -17436,12 +17436,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>8700</t>
+          <t>7637</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>20784</t>
+          <t>20142</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -17451,12 +17451,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>15,31%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -17471,12 +17471,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>17084</t>
+          <t>18026</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>33511</t>
+          <t>33082</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -17486,12 +17486,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>14,27%</t>
         </is>
       </c>
     </row>
@@ -17514,12 +17514,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>70726</t>
+          <t>71288</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>84759</t>
+          <t>84744</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -17529,12 +17529,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>70,5%</t>
+          <t>71,06%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>84,49%</t>
+          <t>84,48%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -17549,12 +17549,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>85091</t>
+          <t>84853</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>104228</t>
+          <t>104410</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -17564,12 +17564,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>64,66%</t>
+          <t>64,48%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>79,21%</t>
+          <t>79,34%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -17584,12 +17584,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>161722</t>
+          <t>162218</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>186303</t>
+          <t>185488</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -17599,12 +17599,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>69,74%</t>
+          <t>69,95%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>80,34%</t>
+          <t>79,98%</t>
         </is>
       </c>
     </row>
@@ -17627,12 +17627,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>6111</t>
+          <t>5958</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>16241</t>
+          <t>16520</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -17642,12 +17642,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>16,47%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -17662,12 +17662,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>15913</t>
+          <t>15061</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>32454</t>
+          <t>33374</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -17677,12 +17677,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>24,66%</t>
+          <t>25,36%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -17697,12 +17697,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>24196</t>
+          <t>24229</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>44452</t>
+          <t>43879</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -17712,12 +17712,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>19,17%</t>
+          <t>18,92%</t>
         </is>
       </c>
     </row>
